--- a/output/看屋檢查清單_新北建案_2026-09-04_二_建商與代銷.xlsx
+++ b/output/看屋檢查清單_新北建案_2026-09-04_二_建商與代銷.xlsx
@@ -231,7 +231,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>資料搜尋日期：2026-09-04　|　來源：591新建案／實價登錄、樂居、樂屋網、5168、住展、永慶、信義、PLEX、Mobile01、各建商官網、看屋部落格、新北市／台北市政府圖資　|　共用說明：①貸款試算＝貸8成/30年/利率2.5%（2026年五大行庫2.3~2.6%）；新青安3.0首購約1.775%、上限1,000萬 ②稅費＝契稅(房屋評定現值×6%)＋印花稅0.1%＋代書費1.5~2萬＋規費0.1%，概估總價1~1.5% ③預售屋法定保固：結構15年、固定建材設備1年，自交屋日起算 ④預售屋履約保證五擇一：價金返還保證／價金信託／不動產開發信託／同業連帶擔保／公會連帶保證 ⑤斷層：台北盆地列冊活動斷層僅山腳斷層(第二類，約1萬年前活動)，位於盆地西北側樹林—北投—金山一線 ⑥土壤液化：新北市已公布14區1/2500中級圖資(第1期板橋/新莊/三重/蘆洲/泰山/五股，第2期中和/永和/土城/鶯歌/三峽/樹林/新店/汐止)，查詢 liquid.net.tw/cgs/Web/Map.aspx；台北市查詢 soil.taipei（1/5000） ⑦淹水潛勢：第三代淹水潛勢圖（103-105年製），假設24小時降雨300/450/600mm之最大淹水深度，查詢國家災害防救科技中心 dmap.ncdr.nat.gov.tw；新北市水利局亦提供潛勢區/低窪區/洪氾區查詢 ⑧治安：引用網路整理之113年(2024)新北市各區犯罪率分級，非警政署原始表，僅供相對比較 ⑨【現場確認】標記＝公開資料查無、須至接待中心索取或調謄本之項目</t>
+          <t>資料搜尋日期：2026-09-04　|　來源：591／樂居／樂屋網／5168／住展／Mobile01／建商官網／政府圖資　|　【試算】貸8成30年2.5%；新青安1.775%上限1000萬｜稅費≒總價1~1.5%｜保固：結構15年、設備1年（自交屋起）｜履約保證法定五擇一｜斷層：北盆地僅山腳斷層(第二類)　|　【現場確認】＝公開資料查無，須向代銷索取或調謄本　|　查詢：土壤液化 liquid.net.tw／soil.taipei；淹水 dmap.ncdr.nat.gov.tw；新北液化圖資第1期板橋三重等、第2期中和土城新店等　|　治安為網路整理之113年新北各區犯罪率分級，非警政署原表　|　!＝風險提醒　+＝正面條件（原⚠️／✅）</t>
         </is>
       </c>
     </row>
@@ -319,9 +319,8 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>茂德建設（茂德機構）：2001年新莊歐風地標案起家，2010年後推萬坪造鎮大案
-代表作：板橋「超級城市SUPER 1~5」、蘆洲捷運聯開「希望城市」、三重「都廳大院」、土城「紅布朗花園」
-各大重劃區推案逾30案；2022年推案量約645億元，居北台灣建商第2名</t>
+          <t>茂德建設：2001年新莊歐風地標案起家，2010年後推萬坪造鎮大案
+2022年推案量約645億元，居北台灣建商第2名</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -338,7 +337,6 @@
         <is>
           <t>瓏山林企業（瓏山林集團，林榮三家族）：長期推案於台北、新北
 內湖代表作：瓏山林藝術館
-其他知名案：四季紐約（乙種工業區住宅案）
 本案規模：基地1,764.2坪，A/B/C棟地上5層住家＋D棟車塔，195戶住家＋1戶店面</t>
         </is>
       </c>
@@ -351,7 +349,6 @@
       <c r="I5" s="8" t="inlineStr">
         <is>
           <t>中德建設（茂德機構）：茂德集團旗下公司
-茂德機構代表作：板橋「超級城市SUPER 1~5」、蘆洲捷運聯開「希望城市」、三重「都廳大院」、土城「紅布朗花園」；各大重劃區推案逾30案
 2022年茂德推案量約645億元，居北台灣建商第2名</t>
         </is>
       </c>
@@ -367,14 +364,6 @@
         <is>
           <r>
             <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">未上市櫃，無公開財報或信用評等可查
-</t>
-          </r>
-          <r>
-            <rPr>
               <b val="1"/>
               <color rgb="00C00000"/>
               <sz val="10"/>
@@ -392,70 +381,35 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">未上市櫃，無公開信用評等
-推案規模為北台灣前段（2022年約645億、第2名），獵地與去化能力強
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠️規模大不等於施工品質好，兩者需分開評估</t>
-          </r>
+          <t>推案規模為北台灣前段（2022年約645億、第2名），獵地與去化能力強</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>新濠建設事業（新濠營造）：未上市櫃，無公開信用評等
-推案區域涵蓋台北市、新莊、板橋、三重、土城、淡水；三重左岸即規劃4案
+          <t>新濠建設事業（新濠營造）：；三重左岸即規劃4案
 同集團新濠岳申請耐震標章，營造實力獲市場正面評價</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>新濠建設事業股份有限公司：未上市櫃，無公開信用評等
-本案申請耐震標章（國家級四大標章之一），營造實力獲市場正面評價
-推案區域涵蓋台北市、新莊、板橋、三重、土城、淡水</t>
+          <t>新濠建設事業股份有限公司：本案申請耐震標章（國家級四大標章之一），營造實力獲市場正面評價</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
           <t>瓏山林建設股份有限公司，負責人林鴻堯，登記於台北市松山區民生東路3段109號18樓
-集團資源雄厚（林榮三家族），但消費爭議紀錄多
-無公開信用評等</t>
+集團資源雄厚（林榮三家族），但消費爭議紀錄多</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
           <t>將捷建設（將捷集團）：2024年10月21日登錄興櫃股票買賣，財務資訊將逐步公開
-由建築師林長勲創辦，逾30年建築事業；提供土地開發、設計、BIM、營造、室內裝修至資產管理一條龍服務
 曾獲台北城都市設計景觀大獎、2008年第一屆全國都市設計大獎（北福大稻埕）</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">未上市櫃，無公開信用評等
-母集團推案規模為北台灣前段，土地與資金部位充足
-</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠️推案規模大不等於施工品質好，兩者需分開評估</t>
-          </r>
+          <t>母集團推案規模為北台灣前段，土地與資金部位充足</t>
         </is>
       </c>
     </row>
@@ -470,14 +424,6 @@
         <is>
           <r>
             <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>公開搜尋未見安豐建設／安豐營造之重大消保或工安糾紛報導
-「未查到」不等於「沒有」，</t>
-          </r>
-          <r>
-            <rPr>
               <b val="1"/>
               <color rgb="00C00000"/>
               <sz val="10"/>
@@ -507,9 +453,91 @@
               <color rgb="FF000000"/>
               <sz val="10"/>
             </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>【現場確認】</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>強烈建議走訪其已交屋社區詢問住戶維修處理情形</t>
+          </r>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>現有建案亦無明顯負評
+市場評價：不二價與階梯式向上調價政策執行嚴格（對買方議價空間不利，非品質問題）</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>現有建案無明顯負評</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>⚠️⚠️本表最重大之建商負面紀錄，購買前務必詳讀：</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
             <t xml:space="preserve">
-媒體與社群指出其過往有公安意外、漏水案件、社區維修糾紛，屢次登上討論榜
-另有「江翠ONE」拋售潮、177億封口爭議等報導，建商評價兩極化
+→</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>【現場確認】</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>務必逐項核對權狀、使用分區、公設項目與車位產權登記方式</t>
+          </r>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>集團經營風格自述為「不貪心、量力而為、沒有賭性」</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>⚠️重大負面：中德建設與茂德建設、寶德建設、精業建設、漢翔建設同被房產評論者Sway列入「不推薦建商」名單</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
 </t>
           </r>
           <r>
@@ -525,143 +553,7 @@
               <color rgb="FF000000"/>
               <sz val="10"/>
             </rPr>
-            <t>強烈建議實地走訪其已交屋社區詢問住戶維修處理情形</t>
-          </r>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>公開搜尋未見新濠建設之重大消保或工安糾紛報導，現有建案亦無明顯負評
-市場評價：不二價與階梯式向上調價政策執行嚴格（對買方議價空間不利，非品質問題）
-「未查到」不等於「沒有」，</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【現場確認】</t>
-          </r>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>公開搜尋未見新濠建設之重大消保或工安糾紛報導，現有建案無明顯負評
-市場評價：不二價與階梯式調價執行嚴格
-「未查到」不等於「沒有」，</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【現場確認】</t>
-          </r>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠️⚠️本表最重大之建商負面紀錄，購買前務必詳讀：</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-①瓏山林藝術館（內湖）公設糾紛：契約未載明車道公設須另計費，交屋後要求約300戶住戶分攤1億5千萬元，公平會認定違反定型化契約，重罰1,200萬元（2011年）
-②同案廣告不實：銷售DM之飯店泳池SPA未興建，地下2樓豪華泳池係停車執照違法改建，建管處開罰6萬元；公設比坪數誤差逾2%（2010年）
-③四季紐約工業宅：陽台外推、乙種工業區不得作住宅，遭公平會裁罰550萬元，總銷約45億元
-④2014年巢運點名瓏山林為「最大黑心建商」；媒體評為「前科累累的建商」
-→</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【現場確認】</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>務必逐項核對權狀、使用分區、公設項目與車位產權登記方式</t>
-          </r>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>公開搜尋未見將捷建設之重大消保、工安或訴訟報導
-集團經營風格自述為「不貪心、量力而為、沒有賭性」
-「未查到」不等於「沒有」，</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【現場確認】</t>
-          </r>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠️重大負面：中德建設與茂德建設、寶德建設、精業建設、漢翔建設同被房產評論者Sway列入「不推薦建商」名單</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-茂德機構相關報導指其過往有公安意外、漏水案件、社區維修糾紛，屢次登上討論榜；另有「江翠ONE」拋售潮、177億封口爭議等報導
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【現場確認】</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>強烈建議實地走訪茂德／中德已交屋社區詢問住戶維修處理情形</t>
+            <t>強烈建議走訪茂德／中德已交屋社區詢問住戶維修處理情形</t>
           </r>
         </is>
       </c>
@@ -755,19 +647,10 @@
         <is>
           <r>
             <rPr>
-              <b val="1"/>
-              <color rgb="00BF8F00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【試算】</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">預售屋法定保固：結構15年、固定建材與設備1年，自交屋日起算
-本案未見額外延長保固之公開承諾（對照：新濠岳提供10年防水保固）
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">本案未見額外延長保固之公開承諾（對照：新濠岳提供10年防水保固）
 </t>
           </r>
           <r>
@@ -842,66 +725,13 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>預售屋依法須採五擇一（價金返還／價金信託／不動產開發信託／同業連帶擔保／公會連帶保證）
-本案為捷運局聯開案，實務上多採不動產開發信託
-確切方式與信託銀行</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【現場確認】</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>，並要求載明於契約</t>
-          </r>
+          <t>預售屋依法須採五擇一（價金返還／價金信託／不動產開發信託／同業連帶擔保／公會連帶保證）
+本案為捷運局聯開案，實務上多採不動產開發信託</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00BF8F00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【試算】</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>預售屋依法五擇一（價金返還／價金信託／不動產開發信託／同業連帶擔保／公會連帶保證）
-大型造鎮案實務上多採不動產開發信託
-確切方式與信託銀行</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【現場確認】</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>，並要求載明於契約</t>
-          </r>
+          <t>大型造鎮案實務上多採不動產開發信託</t>
         </is>
       </c>
     </row>
@@ -921,7 +751,6 @@
             </rPr>
             <t xml:space="preserve">Mobile01 討論串評價分歧：
 優點－大廳鍍鈦/大板磚/石材、陽台多且大、落地窗隔音佳、地點與價格具競爭力
-缺點－新埔5號出口一帶商家少覓食不便、高架橋噪音明顯
 </t>
           </r>
           <r>
@@ -963,52 +792,14 @@
       <c r="H11" s="8" t="inlineStr">
         <is>
           <t>樂居看屋筆記、林保宏、蔡小妞依玲等均有專文
-優點：出站即到家、格局方正、1房也有大陽台、客廳與主次臥皆落地窗、機能成熟
 缺點：面景平路戶型有車流聲；高架捷運煞車聲/低頻震動；景平路長年工程</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Mobile01、看房部落格評價分歧：
+          <t>Mobile01、看房部落格評價分歧：
 優點－基地大（近3,300坪）、公設豐富、緊鄰Y23與銀新未來城題材
-缺點－</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="001F4E78"/>
-              <sz val="10"/>
-            </rPr>
-            <t>多數格局不佳</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>（室內14坪隔3房、暗廳）、</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="001F4E78"/>
-              <sz val="10"/>
-            </rPr>
-            <t>戶數太多不給客變</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>、
-　　　D2戶21坪有長走道浪費空間且廚房對臥室門</t>
-          </r>
+D2戶21坪有長走道浪費空間且廚房對臥室門</t>
         </is>
       </c>
     </row>
